--- a/Invoices_Data.xlsx
+++ b/Invoices_Data.xlsx
@@ -481,12 +481,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INV-20260829145854</t>
+          <t>INV-20260831151150</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>29-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Heathrow</t>
+          <t>12 Little Venice</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
